--- a/Data/ready_for_classifier.xlsx
+++ b/Data/ready_for_classifier.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -50,13 +53,19 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -78,13 +87,13 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -600,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>4</v>
@@ -645,7 +654,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0.75</v>
@@ -654,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0</v>
@@ -672,7 +681,7 @@
         <v>0</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="4">
@@ -705,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.3333</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0.6667</v>
@@ -714,7 +723,7 @@
         <v>0.5</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -732,7 +741,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="5">
@@ -774,7 +783,7 @@
         <v>0.3889</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.5556</v>
+        <v>0.7778</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0</v>
@@ -789,10 +798,10 @@
         <v>3.8889</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0.1</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.3</v>
+        <v>0.2857</v>
       </c>
     </row>
     <row r="6">
@@ -834,7 +843,7 @@
         <v>0.5714</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.2143</v>
+        <v>0.6429</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -849,7 +858,7 @@
         <v>3.6429</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0</v>
+        <v>0.1111</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>0.3333</v>
@@ -894,7 +903,7 @@
         <v>0.8333</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
@@ -909,10 +918,10 @@
         <v>4</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.3333</v>
+        <v>0.2222</v>
       </c>
     </row>
     <row r="8">
@@ -954,7 +963,7 @@
         <v>0.2727</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.1818</v>
+        <v>0.2727</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -969,10 +978,10 @@
         <v>5.1818</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="9">
@@ -1005,7 +1014,7 @@
         <v>0.1667</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.1667</v>
+        <v>0.0833</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.3333</v>
@@ -1014,7 +1023,7 @@
         <v>0.6667</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.0833</v>
+        <v>0.3333</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>0</v>
@@ -1029,10 +1038,10 @@
         <v>4.6667</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="10">
@@ -1134,7 +1143,7 @@
         <v>0.2222</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.2222</v>
+        <v>0.3333</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
@@ -1194,7 +1203,7 @@
         <v>0.5</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1314,7 +1323,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1329,7 +1338,7 @@
         <v>3.5</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>0</v>
@@ -1365,7 +1374,7 @@
         <v>0.1333</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.1333</v>
+        <v>0.0667</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0.4</v>
@@ -1374,7 +1383,7 @@
         <v>0.6</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.1333</v>
+        <v>0.4</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>0</v>
@@ -1389,10 +1398,10 @@
         <v>3.7333</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>0</v>
+        <v>0.1667</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>1</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="16">
@@ -1434,7 +1443,7 @@
         <v>0.5</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1449,10 +1458,10 @@
         <v>4</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="17">
@@ -1494,7 +1503,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>0</v>
@@ -1509,10 +1518,10 @@
         <v>3.75</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="18">
@@ -1554,7 +1563,7 @@
         <v>0.5</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1569,7 +1578,7 @@
         <v>3.3333</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="P18" s="2" t="n">
         <v>0</v>
@@ -1605,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.6667</v>
+        <v>0.3333</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>0.6667</v>
@@ -1614,7 +1623,7 @@
         <v>0.5</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>0</v>
@@ -1734,7 +1743,7 @@
         <v>0.8571</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.5714</v>
+        <v>0.7143</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
@@ -1749,10 +1758,10 @@
         <v>4.4286</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="22">
@@ -1785,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.1667</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>0.5</v>
@@ -1794,7 +1803,7 @@
         <v>0.8333</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.5833</v>
+        <v>1.0833</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1809,10 +1818,10 @@
         <v>4</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>0</v>
+        <v>0.0769</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>0.4286</v>
+        <v>0.1538</v>
       </c>
     </row>
     <row r="23">
@@ -1845,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.6667</v>
+        <v>0.3333</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>0.6667</v>
@@ -1854,7 +1863,7 @@
         <v>0.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>0</v>
@@ -1914,7 +1923,7 @@
         <v>0.5</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.3333</v>
+        <v>1</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1932,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="25">
@@ -1974,7 +1983,7 @@
         <v>0.3333</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0</v>
+        <v>0.1111</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>0</v>
@@ -2034,7 +2043,7 @@
         <v>0.4444</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.4444</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -2052,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2103,7 @@
         <v>0.5</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0</v>
+        <v>0.6667</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>0</v>
@@ -2274,7 +2283,7 @@
         <v>0.4167</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.6667</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2394,7 +2403,7 @@
         <v>0.2857</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.2857</v>
+        <v>0.3571</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2454,7 +2463,7 @@
         <v>0.6</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>0</v>
@@ -2514,7 +2523,7 @@
         <v>0.4286</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.1429</v>
+        <v>0.2857</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2634,7 +2643,7 @@
         <v>0.5</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2694,7 +2703,7 @@
         <v>0.75</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>0</v>
@@ -2712,7 +2721,7 @@
         <v>0</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="38">
@@ -2754,7 +2763,7 @@
         <v>0.8571</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.5714</v>
+        <v>0.7143</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2769,10 +2778,10 @@
         <v>4</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="39">
@@ -2874,7 +2883,7 @@
         <v>0.75</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.8333</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2889,10 +2898,10 @@
         <v>5.0833</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>0.375</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="41">
@@ -2934,7 +2943,7 @@
         <v>0.3846</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.1538</v>
+        <v>0.2308</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
@@ -2952,7 +2961,7 @@
         <v>0</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="42">
@@ -2985,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.1429</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>0.2143</v>
@@ -2994,7 +3003,7 @@
         <v>0.3571</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.1429</v>
+        <v>0.5</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -3012,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4286</v>
       </c>
     </row>
     <row r="43">
@@ -3054,7 +3063,7 @@
         <v>0.2941</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.2353</v>
+        <v>0.2941</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>0</v>
@@ -3072,7 +3081,7 @@
         <v>0</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="44">
@@ -3105,7 +3114,7 @@
         <v>0.0769</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.1538</v>
+        <v>0.0769</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>0.5385</v>
@@ -3114,7 +3123,7 @@
         <v>0.6923</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.4615</v>
+        <v>0.7692</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -3132,7 +3141,7 @@
         <v>0</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>0.1667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="45">
@@ -3234,7 +3243,7 @@
         <v>0.5</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.1667</v>
+        <v>0.6667</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -3252,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="47">
@@ -3285,7 +3294,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.1667</v>
+        <v>0.0833</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>0.4167</v>
@@ -3294,13 +3303,13 @@
         <v>1</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.75</v>
+        <v>1.0833</v>
       </c>
       <c r="K47" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.1667</v>
+        <v>1</v>
       </c>
       <c r="M47" s="3" t="n">
         <v>12</v>
@@ -3309,10 +3318,10 @@
         <v>4.0833</v>
       </c>
       <c r="O47" s="3" t="n">
-        <v>0.1111</v>
+        <v>0.0769</v>
       </c>
       <c r="P47" s="3" t="n">
-        <v>0</v>
+        <v>0.0769</v>
       </c>
     </row>
     <row r="48">
@@ -3354,7 +3363,7 @@
         <v>0.7692</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.6923</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3369,10 +3378,10 @@
         <v>4.4615</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>0</v>
+        <v>0.1111</v>
       </c>
       <c r="P48" s="2" t="n">
-        <v>0.125</v>
+        <v>0.1111</v>
       </c>
     </row>
     <row r="49">
@@ -3414,7 +3423,7 @@
         <v>0.6667</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5833</v>
       </c>
       <c r="K49" s="3" t="n">
         <v>0</v>
@@ -3429,10 +3438,10 @@
         <v>4.5833</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>0.3333</v>
+        <v>0.2857</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>0.1667</v>
+        <v>0.1429</v>
       </c>
     </row>
     <row r="50">
@@ -3465,7 +3474,7 @@
         <v>0.1429</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.3571</v>
+        <v>0.2143</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>0.3571</v>
@@ -3474,7 +3483,7 @@
         <v>0.7143</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.7143</v>
+        <v>1</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3489,10 +3498,10 @@
         <v>3.5714</v>
       </c>
       <c r="O50" s="2" t="n">
-        <v>0.1</v>
+        <v>0.2857</v>
       </c>
       <c r="P50" s="2" t="n">
-        <v>0.3</v>
+        <v>0.2143</v>
       </c>
     </row>
     <row r="51">
@@ -3534,7 +3543,7 @@
         <v>0.5294</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.5881999999999999</v>
+        <v>1</v>
       </c>
       <c r="K51" s="3" t="n">
         <v>0</v>
@@ -3552,7 +3561,7 @@
         <v>0</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>0.3</v>
+        <v>0.1765</v>
       </c>
     </row>
     <row r="52">
@@ -3594,7 +3603,7 @@
         <v>0.9231</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4615</v>
+        <v>0.7692</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3609,10 +3618,10 @@
         <v>3.7692</v>
       </c>
       <c r="O52" s="2" t="n">
-        <v>0.1667</v>
+        <v>0.1</v>
       </c>
       <c r="P52" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="53">
@@ -3654,7 +3663,7 @@
         <v>0.7692</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.4615</v>
+        <v>0.5385</v>
       </c>
       <c r="K53" s="3" t="n">
         <v>0</v>
@@ -3669,10 +3678,10 @@
         <v>4.1538</v>
       </c>
       <c r="O53" s="3" t="n">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
       <c r="P53" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4286</v>
       </c>
     </row>
     <row r="54">
@@ -3714,7 +3723,7 @@
         <v>0.9231</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.6923</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3729,10 +3738,10 @@
         <v>4.2308</v>
       </c>
       <c r="O54" s="2" t="n">
-        <v>0.125</v>
+        <v>0.2222</v>
       </c>
       <c r="P54" s="2" t="n">
-        <v>0.125</v>
+        <v>0.1111</v>
       </c>
     </row>
     <row r="55">
@@ -3834,13 +3843,13 @@
         <v>0.4286</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0</v>
+        <v>0.2143</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M56" s="2" t="n">
         <v>14</v>
@@ -3849,7 +3858,7 @@
         <v>3.5714</v>
       </c>
       <c r="O56" s="2" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="P56" s="2" t="n">
         <v>0</v>
@@ -3894,7 +3903,7 @@
         <v>0.4615</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.9231</v>
       </c>
       <c r="K57" s="3" t="n">
         <v>0</v>
@@ -3909,10 +3918,10 @@
         <v>3.6923</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>0</v>
+        <v>0.0833</v>
       </c>
       <c r="P57" s="3" t="n">
-        <v>0.25</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="58">
@@ -3954,7 +3963,7 @@
         <v>1</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3969,10 +3978,10 @@
         <v>4.8</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>0.125</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="P58" s="2" t="n">
-        <v>0.125</v>
+        <v>0.1818</v>
       </c>
     </row>
     <row r="59">
@@ -4014,7 +4023,7 @@
         <v>0.4167</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.0833</v>
+        <v>0.25</v>
       </c>
       <c r="K59" s="3" t="n">
         <v>0</v>
@@ -4032,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="60">
@@ -4074,7 +4083,7 @@
         <v>0.3333</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.2222</v>
+        <v>0.4444</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -4134,13 +4143,13 @@
         <v>0.5</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
       <c r="K61" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.1667</v>
+        <v>1</v>
       </c>
       <c r="M61" s="3" t="n">
         <v>6</v>
@@ -4152,7 +4161,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="62">
@@ -4254,7 +4263,7 @@
         <v>0.5</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="K63" s="3" t="n">
         <v>0</v>
@@ -4272,7 +4281,7 @@
         <v>0</v>
       </c>
       <c r="P63" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="64">
@@ -4320,7 +4329,7 @@
         <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0.1667</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="n">
         <v>6</v>
@@ -4332,7 +4341,7 @@
         <v>0</v>
       </c>
       <c r="P64" s="2" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4374,7 +4383,7 @@
         <v>0.5</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K65" s="3" t="n">
         <v>0</v>
@@ -4440,7 +4449,7 @@
         <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
       <c r="M66" s="2" t="n">
         <v>3</v>
@@ -4494,7 +4503,7 @@
         <v>1</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="K67" s="3" t="n">
         <v>0</v>
@@ -4509,10 +4518,10 @@
         <v>3.25</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="68">
@@ -4554,7 +4563,7 @@
         <v>0.8333</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4572,7 +4581,7 @@
         <v>0</v>
       </c>
       <c r="P68" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="69">
@@ -4674,7 +4683,7 @@
         <v>0.5</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.6667</v>
+        <v>1.3333</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4734,7 +4743,7 @@
         <v>0.4</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K71" s="3" t="n">
         <v>0</v>
@@ -4794,7 +4803,7 @@
         <v>1</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4812,7 +4821,7 @@
         <v>0</v>
       </c>
       <c r="P72" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="73">
@@ -4854,7 +4863,7 @@
         <v>0.875</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.5</v>
+        <v>1.125</v>
       </c>
       <c r="K73" s="3" t="n">
         <v>0</v>
@@ -4872,7 +4881,7 @@
         <v>0</v>
       </c>
       <c r="P73" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="74">
@@ -4905,7 +4914,7 @@
         <v>0.25</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>0</v>
@@ -4920,7 +4929,7 @@
         <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6667</v>
       </c>
       <c r="M74" s="2" t="n">
         <v>4</v>
@@ -5094,7 +5103,7 @@
         <v>0.6153999999999999</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>0.4615</v>
+        <v>0.5385</v>
       </c>
       <c r="K77" s="3" t="n">
         <v>0</v>
@@ -5112,7 +5121,7 @@
         <v>0</v>
       </c>
       <c r="P77" s="3" t="n">
-        <v>0.3333</v>
+        <v>0.2857</v>
       </c>
     </row>
     <row r="78">
@@ -5154,7 +5163,7 @@
         <v>1</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.4286</v>
+        <v>0.5714</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -5169,7 +5178,7 @@
         <v>5.2857</v>
       </c>
       <c r="O78" s="2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P78" s="2" t="n">
         <v>0</v>
@@ -5274,13 +5283,13 @@
         <v>0.9167</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0.25</v>
+        <v>0.6667</v>
       </c>
       <c r="M80" s="2" t="n">
         <v>12</v>
@@ -5289,10 +5298,10 @@
         <v>4.4167</v>
       </c>
       <c r="O80" s="2" t="n">
-        <v>0</v>
+        <v>0.1667</v>
       </c>
       <c r="P80" s="2" t="n">
-        <v>0.1111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5334,7 +5343,7 @@
         <v>1</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K81" s="3" t="n">
         <v>0</v>
@@ -5352,7 +5361,7 @@
         <v>0</v>
       </c>
       <c r="P81" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="82">
@@ -5385,7 +5394,7 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.2222</v>
+        <v>0.1111</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>0</v>
@@ -5394,7 +5403,7 @@
         <v>0.1111</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0</v>
+        <v>0.1111</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -5445,7 +5454,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.1538</v>
+        <v>0.0769</v>
       </c>
       <c r="H83" s="3" t="n">
         <v>0</v>
@@ -5454,7 +5463,7 @@
         <v>0.0769</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0</v>
+        <v>0.0769</v>
       </c>
       <c r="K83" s="3" t="n">
         <v>0</v>
@@ -5574,13 +5583,13 @@
         <v>0.7692</v>
       </c>
       <c r="J85" s="3" t="n">
+        <v>1.3077</v>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="K85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="3" t="n">
-        <v>0.0769</v>
       </c>
       <c r="M85" s="3" t="n">
         <v>13</v>
@@ -5592,7 +5601,7 @@
         <v>0</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>0.3077</v>
+        <v>0.2941</v>
       </c>
     </row>
     <row r="86">
@@ -5694,7 +5703,7 @@
         <v>0.5556</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>0.6667</v>
+        <v>0.7778</v>
       </c>
       <c r="K87" s="3" t="n">
         <v>0</v>
@@ -5712,7 +5721,7 @@
         <v>0</v>
       </c>
       <c r="P87" s="3" t="n">
-        <v>0.1667</v>
+        <v>0.2857</v>
       </c>
     </row>
     <row r="88">
@@ -5865,7 +5874,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.1667</v>
+        <v>0.0833</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>0.0833</v>
@@ -5874,7 +5883,7 @@
         <v>0.4167</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.4167</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5889,7 +5898,7 @@
         <v>4.3333</v>
       </c>
       <c r="O90" s="2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P90" s="2" t="n">
         <v>0</v>
@@ -5994,7 +6003,7 @@
         <v>0.6667</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -6012,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="P92" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="93">
@@ -6054,13 +6063,13 @@
         <v>0.9</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K93" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L93" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="M93" s="3" t="n">
         <v>10</v>
@@ -6072,7 +6081,7 @@
         <v>0</v>
       </c>
       <c r="P93" s="3" t="n">
-        <v>0.25</v>
+        <v>0.1111</v>
       </c>
     </row>
     <row r="94">
@@ -6120,7 +6129,7 @@
         <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M94" s="2" t="n">
         <v>10</v>
@@ -6174,7 +6183,7 @@
         <v>0.5556</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>0.4444</v>
+        <v>0.6667</v>
       </c>
       <c r="K95" s="3" t="n">
         <v>0</v>
@@ -6189,10 +6198,10 @@
         <v>4.7778</v>
       </c>
       <c r="O95" s="3" t="n">
-        <v>0</v>
+        <v>0.1667</v>
       </c>
       <c r="P95" s="3" t="n">
-        <v>0.25</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="96">
@@ -6285,7 +6294,7 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>0.5714</v>
+        <v>0.3571</v>
       </c>
       <c r="H97" s="3" t="n">
         <v>0.5</v>
@@ -6294,13 +6303,13 @@
         <v>0.7857</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>0.2857</v>
+        <v>0.5</v>
       </c>
       <c r="K97" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L97" s="3" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.1667</v>
       </c>
       <c r="M97" s="3" t="n">
         <v>14</v>
@@ -6309,10 +6318,10 @@
         <v>4.5714</v>
       </c>
       <c r="O97" s="3" t="n">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
       <c r="P97" s="3" t="n">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
     </row>
     <row r="98">
@@ -6345,7 +6354,7 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.1818</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="H98" s="2" t="n">
         <v>0.2727</v>
@@ -6354,7 +6363,7 @@
         <v>0.9091</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.3636</v>
+        <v>0.4545</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -6369,7 +6378,7 @@
         <v>3.6364</v>
       </c>
       <c r="O98" s="2" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="P98" s="2" t="n">
         <v>0</v>
@@ -6414,7 +6423,7 @@
         <v>0.6923</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.6923</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>0</v>
@@ -6429,7 +6438,7 @@
         <v>4</v>
       </c>
       <c r="O99" s="3" t="n">
-        <v>0.125</v>
+        <v>0.2222</v>
       </c>
       <c r="P99" s="3" t="n">
         <v>0</v>
@@ -6474,7 +6483,7 @@
         <v>0.5</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -6492,7 +6501,7 @@
         <v>0</v>
       </c>
       <c r="P100" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="101">
@@ -6534,7 +6543,7 @@
         <v>1</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="K101" s="3" t="n">
         <v>0</v>
@@ -6549,10 +6558,10 @@
         <v>4</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0.2</v>
+        <v>0.1667</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -6594,7 +6603,7 @@
         <v>0.8333</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.5556</v>
+        <v>0.6111</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -6609,10 +6618,10 @@
         <v>3.3333</v>
       </c>
       <c r="O102" s="2" t="n">
-        <v>0.1</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="P102" s="2" t="n">
-        <v>0.2</v>
+        <v>0.1818</v>
       </c>
     </row>
     <row r="103">
@@ -6654,7 +6663,7 @@
         <v>0.8462</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0.7692</v>
+        <v>0.8462</v>
       </c>
       <c r="K103" s="3" t="n">
         <v>0</v>
@@ -6669,10 +6678,10 @@
         <v>4.0769</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>0</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="P103" s="3" t="n">
-        <v>0.2</v>
+        <v>0.1818</v>
       </c>
     </row>
     <row r="104">
@@ -6705,7 +6714,7 @@
         <v>0.0833</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.5833</v>
+        <v>0.3333</v>
       </c>
       <c r="H104" s="2" t="n">
         <v>0.5833</v>
@@ -6714,13 +6723,13 @@
         <v>1</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6667</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>0.1667</v>
+        <v>0.4</v>
       </c>
       <c r="M104" s="2" t="n">
         <v>12</v>
@@ -6729,10 +6738,10 @@
         <v>4.25</v>
       </c>
       <c r="O104" s="2" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="P104" s="2" t="n">
-        <v>0.1667</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="105">
@@ -6774,7 +6783,7 @@
         <v>0.4</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K105" s="3" t="n">
         <v>0</v>
@@ -6792,7 +6801,7 @@
         <v>0</v>
       </c>
       <c r="P105" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="106">
@@ -6894,7 +6903,7 @@
         <v>1</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
       <c r="K107" s="3" t="n">
         <v>0</v>
@@ -6909,7 +6918,7 @@
         <v>3.625</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0.3333</v>
+        <v>0.2</v>
       </c>
       <c r="P107" s="3" t="n">
         <v>0</v>
@@ -7014,7 +7023,7 @@
         <v>0.875</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="K109" s="3" t="n">
         <v>0</v>
@@ -7032,7 +7041,7 @@
         <v>0</v>
       </c>
       <c r="P109" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="110">
@@ -7080,7 +7089,7 @@
         <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="n">
         <v>4</v>
@@ -7125,7 +7134,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0.5714</v>
+        <v>0.4286</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0.2857</v>
@@ -7134,7 +7143,7 @@
         <v>1</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0.2857</v>
+        <v>0.4286</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>0</v>
@@ -7149,10 +7158,10 @@
         <v>2.8571</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="112">
@@ -7494,13 +7503,13 @@
         <v>0.9</v>
       </c>
       <c r="J117" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K117" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L117" s="3" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="M117" s="3" t="n">
         <v>10</v>
@@ -7512,7 +7521,7 @@
         <v>0</v>
       </c>
       <c r="P117" s="3" t="n">
-        <v>0.0833</v>
+        <v>0.0769</v>
       </c>
     </row>
     <row r="118">
@@ -7554,13 +7563,13 @@
         <v>0.4167</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.4167</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L118" s="2" t="n">
-        <v>0.1667</v>
+        <v>1</v>
       </c>
       <c r="M118" s="2" t="n">
         <v>12</v>
@@ -7680,7 +7689,7 @@
         <v>0</v>
       </c>
       <c r="L120" s="2" t="n">
-        <v>0.1818</v>
+        <v>0.5</v>
       </c>
       <c r="M120" s="2" t="n">
         <v>11</v>
@@ -7734,13 +7743,13 @@
         <v>0.8182</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0.9091</v>
+        <v>1.0909</v>
       </c>
       <c r="K121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0.5455</v>
+        <v>0.8</v>
       </c>
       <c r="M121" s="3" t="n">
         <v>11</v>
@@ -7749,7 +7758,7 @@
         <v>5.4545</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0.2</v>
+        <v>0.1667</v>
       </c>
       <c r="P121" s="3" t="n">
         <v>0</v>
@@ -7794,13 +7803,13 @@
         <v>0.6667</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.8333</v>
+        <v>0.9167</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L122" s="2" t="n">
-        <v>0.1667</v>
+        <v>1</v>
       </c>
       <c r="M122" s="2" t="n">
         <v>12</v>
@@ -7809,10 +7818,10 @@
         <v>4.1667</v>
       </c>
       <c r="O122" s="2" t="n">
-        <v>0.1</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="P122" s="2" t="n">
-        <v>0.1</v>
+        <v>0.09089999999999999</v>
       </c>
     </row>
     <row r="123">
@@ -7965,7 +7974,7 @@
         <v>0.1111</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0.2222</v>
+        <v>0.1111</v>
       </c>
       <c r="H125" s="3" t="n">
         <v>0.7778</v>
@@ -8112,7 +8121,7 @@
         <v>0.1667</v>
       </c>
       <c r="P127" s="3" t="n">
-        <v>0.3333</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="128">
@@ -8280,7 +8289,7 @@
         <v>0</v>
       </c>
       <c r="L130" s="2" t="n">
-        <v>0.1429</v>
+        <v>1</v>
       </c>
       <c r="M130" s="2" t="n">
         <v>7</v>
@@ -8292,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="P130" s="2" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -8352,7 +8361,7 @@
         <v>0</v>
       </c>
       <c r="P131" s="3" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="132">
@@ -8394,7 +8403,7 @@
         <v>0.8571</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.7143</v>
+        <v>0.8571</v>
       </c>
       <c r="K132" s="2" t="n">
         <v>0</v>
@@ -8412,7 +8421,7 @@
         <v>0</v>
       </c>
       <c r="P132" s="2" t="n">
-        <v>0.4</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="133">
@@ -8460,7 +8469,7 @@
         <v>0</v>
       </c>
       <c r="L133" s="3" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="M133" s="3" t="n">
         <v>8</v>
@@ -8472,7 +8481,7 @@
         <v>0</v>
       </c>
       <c r="P133" s="3" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="134">
@@ -8532,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="P134" s="2" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -8592,7 +8601,7 @@
         <v>0</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -8754,7 +8763,7 @@
         <v>0.2222</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.6667</v>
       </c>
       <c r="K138" s="2" t="n">
         <v>0</v>
@@ -8772,7 +8781,7 @@
         <v>0</v>
       </c>
       <c r="P138" s="2" t="n">
-        <v>0</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="139">
@@ -8892,7 +8901,7 @@
         <v>0</v>
       </c>
       <c r="P140" s="2" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="141">
@@ -9180,7 +9189,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="3" t="n">
-        <v>0.1667</v>
+        <v>1</v>
       </c>
       <c r="M145" s="3" t="n">
         <v>6</v>
@@ -9225,7 +9234,7 @@
         <v>0</v>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.1667</v>
       </c>
       <c r="H146" s="2" t="n">
         <v>0.1667</v>
@@ -9234,7 +9243,7 @@
         <v>0.6667</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.1667</v>
+        <v>0.3333</v>
       </c>
       <c r="K146" s="2" t="n">
         <v>0</v>
@@ -9252,7 +9261,7 @@
         <v>0</v>
       </c>
       <c r="P146" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9423,7 @@
         <v>0.8</v>
       </c>
       <c r="J149" s="3" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K149" s="3" t="n">
         <v>0</v>
@@ -9465,7 +9474,7 @@
         <v>0</v>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.1818</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="H150" s="2" t="n">
         <v>0.2727</v>
@@ -9612,7 +9621,7 @@
         <v>0</v>
       </c>
       <c r="P152" s="2" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="153">
@@ -9654,7 +9663,7 @@
         <v>0.4545</v>
       </c>
       <c r="J153" s="3" t="n">
-        <v>0.2727</v>
+        <v>0.3636</v>
       </c>
       <c r="K153" s="3" t="n">
         <v>0</v>
@@ -9672,7 +9681,7 @@
         <v>0</v>
       </c>
       <c r="P153" s="3" t="n">
-        <v>0.3333</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="154">
@@ -9714,7 +9723,7 @@
         <v>0.6923</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>0.2308</v>
+        <v>0.3077</v>
       </c>
       <c r="K154" s="2" t="n">
         <v>0</v>
@@ -9765,7 +9774,7 @@
         <v>0</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>0.1667</v>
+        <v>0.0833</v>
       </c>
       <c r="H155" s="3" t="n">
         <v>0.75</v>
@@ -9792,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="P155" s="3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -9825,7 +9834,7 @@
         <v>0.1429</v>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.2857</v>
+        <v>0.1429</v>
       </c>
       <c r="H156" s="2" t="n">
         <v>0.2857</v>
@@ -9840,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="2" t="n">
-        <v>0.1429</v>
+        <v>0.5</v>
       </c>
       <c r="M156" s="2" t="n">
         <v>7</v>
@@ -9912,7 +9921,7 @@
         <v>0</v>
       </c>
       <c r="P157" s="3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -9960,7 +9969,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="2" t="n">
-        <v>0.0833</v>
+        <v>0.5</v>
       </c>
       <c r="M158" s="2" t="n">
         <v>12</v>
@@ -9972,7 +9981,7 @@
         <v>0</v>
       </c>
       <c r="P158" s="2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -10194,7 +10203,7 @@
         <v>0.5714</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>0.619</v>
+        <v>0.7143</v>
       </c>
       <c r="K162" s="2" t="n">
         <v>0</v>
@@ -10212,7 +10221,7 @@
         <v>0</v>
       </c>
       <c r="P162" s="2" t="n">
-        <v>0.2308</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="163">
@@ -10314,7 +10323,7 @@
         <v>0.7272999999999999</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>0.2727</v>
+        <v>0.3636</v>
       </c>
       <c r="K164" s="2" t="n">
         <v>0</v>
@@ -10332,7 +10341,7 @@
         <v>0</v>
       </c>
       <c r="P164" s="2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="165">
@@ -10494,7 +10503,7 @@
         <v>0.8333</v>
       </c>
       <c r="J167" s="3" t="n">
-        <v>0.1667</v>
+        <v>0.3333</v>
       </c>
       <c r="K167" s="3" t="n">
         <v>0</v>
@@ -10512,7 +10521,7 @@
         <v>0</v>
       </c>
       <c r="P167" s="3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="168">
@@ -10974,7 +10983,7 @@
         <v>1</v>
       </c>
       <c r="J175" s="3" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="K175" s="3" t="n">
         <v>0</v>
@@ -11034,13 +11043,13 @@
         <v>0.75</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="K176" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L176" s="2" t="n">
-        <v>0.0625</v>
+        <v>0.1429</v>
       </c>
       <c r="M176" s="2" t="n">
         <v>16</v>
@@ -11049,10 +11058,10 @@
         <v>4.75</v>
       </c>
       <c r="O176" s="2" t="n">
-        <v>0.125</v>
+        <v>0.3</v>
       </c>
       <c r="P176" s="2" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -11112,7 +11121,7 @@
         <v>0.25</v>
       </c>
       <c r="P177" s="3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -11232,7 +11241,7 @@
         <v>0</v>
       </c>
       <c r="P179" s="3" t="n">
-        <v>0.2857</v>
+        <v>0.2143</v>
       </c>
     </row>
     <row r="180">
@@ -11454,7 +11463,7 @@
         <v>0.5</v>
       </c>
       <c r="J183" s="3" t="n">
-        <v>0.3333</v>
+        <v>0.6667</v>
       </c>
       <c r="K183" s="3" t="n">
         <v>0</v>
@@ -11514,7 +11523,7 @@
         <v>0.75</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K184" s="2" t="n">
         <v>0</v>
@@ -11712,7 +11721,7 @@
         <v>0</v>
       </c>
       <c r="P187" s="3" t="n">
-        <v>0.25</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="188">
@@ -11805,7 +11814,7 @@
         <v>0.2857</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>0.2857</v>
+        <v>0.1429</v>
       </c>
       <c r="H189" s="3" t="n">
         <v>0.1429</v>
@@ -11874,7 +11883,7 @@
         <v>0.8</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="K190" s="2" t="n">
         <v>0</v>
@@ -12012,7 +12021,7 @@
         <v>0</v>
       </c>
       <c r="P192" s="2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -12132,7 +12141,7 @@
         <v>0</v>
       </c>
       <c r="P194" s="2" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="195">
@@ -12192,7 +12201,7 @@
         <v>0</v>
       </c>
       <c r="P195" s="3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -12225,7 +12234,7 @@
         <v>0.2857</v>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.2857</v>
+        <v>0.1429</v>
       </c>
       <c r="H196" s="2" t="n">
         <v>0.1429</v>
@@ -12240,7 +12249,7 @@
         <v>0</v>
       </c>
       <c r="L196" s="2" t="n">
-        <v>0.1429</v>
+        <v>0.3333</v>
       </c>
       <c r="M196" s="2" t="n">
         <v>7</v>
@@ -12300,7 +12309,7 @@
         <v>0</v>
       </c>
       <c r="L197" s="3" t="n">
-        <v>0.1667</v>
+        <v>0.5</v>
       </c>
       <c r="M197" s="3" t="n">
         <v>6</v>
@@ -12354,13 +12363,13 @@
         <v>0.8333</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>0.0833</v>
+        <v>0.1667</v>
       </c>
       <c r="K198" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L198" s="2" t="n">
-        <v>0.1667</v>
+        <v>0.4</v>
       </c>
       <c r="M198" s="2" t="n">
         <v>12</v>
@@ -12372,7 +12381,7 @@
         <v>0</v>
       </c>
       <c r="P198" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="199">
@@ -12420,7 +12429,7 @@
         <v>0</v>
       </c>
       <c r="L199" s="3" t="n">
-        <v>0.125</v>
+        <v>0.5</v>
       </c>
       <c r="M199" s="3" t="n">
         <v>8</v>
@@ -12720,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="L204" s="2" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="M204" s="2" t="n">
         <v>4</v>
@@ -13065,7 +13074,7 @@
         <v>0</v>
       </c>
       <c r="G210" s="2" t="n">
-        <v>1.3333</v>
+        <v>0.6667</v>
       </c>
       <c r="H210" s="2" t="n">
         <v>0</v>
@@ -13080,7 +13089,7 @@
         <v>0</v>
       </c>
       <c r="L210" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
       <c r="M210" s="2" t="n">
         <v>3</v>
@@ -13134,7 +13143,7 @@
         <v>1</v>
       </c>
       <c r="J211" s="3" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K211" s="3" t="n">
         <v>0</v>
@@ -13434,7 +13443,7 @@
         <v>0.625</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="K216" s="2" t="n">
         <v>0</v>
@@ -13485,7 +13494,7 @@
         <v>0</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H217" s="3" t="n">
         <v>0.5</v>
@@ -13500,7 +13509,7 @@
         <v>0</v>
       </c>
       <c r="L217" s="3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M217" s="3" t="n">
         <v>4</v>
@@ -13665,7 +13674,7 @@
         <v>0.1429</v>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.2857</v>
+        <v>0.1429</v>
       </c>
       <c r="H220" s="2" t="n">
         <v>0.1429</v>
@@ -13752,7 +13761,7 @@
         <v>0</v>
       </c>
       <c r="P221" s="3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -13854,13 +13863,13 @@
         <v>1</v>
       </c>
       <c r="J223" s="3" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="K223" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L223" s="3" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="M223" s="3" t="n">
         <v>4</v>
@@ -14112,7 +14121,7 @@
         <v>0</v>
       </c>
       <c r="P227" s="3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -14145,7 +14154,7 @@
         <v>0.1111</v>
       </c>
       <c r="G228" s="2" t="n">
-        <v>0.2222</v>
+        <v>0.1111</v>
       </c>
       <c r="H228" s="2" t="n">
         <v>0.3333</v>
@@ -14154,7 +14163,7 @@
         <v>0.6667</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.4444</v>
       </c>
       <c r="K228" s="2" t="n">
         <v>0</v>
@@ -14172,7 +14181,7 @@
         <v>0</v>
       </c>
       <c r="P228" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="229">
@@ -14205,7 +14214,7 @@
         <v>0</v>
       </c>
       <c r="G229" s="3" t="n">
-        <v>0.2857</v>
+        <v>0.1429</v>
       </c>
       <c r="H229" s="3" t="n">
         <v>0.5714</v>
@@ -14274,13 +14283,13 @@
         <v>1</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="K230" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L230" s="2" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="M230" s="2" t="n">
         <v>4</v>
@@ -14292,7 +14301,7 @@
         <v>0</v>
       </c>
       <c r="P230" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="231">
@@ -14325,7 +14334,7 @@
         <v>0.1852</v>
       </c>
       <c r="G231" s="3" t="n">
-        <v>0.2963</v>
+        <v>0.1481</v>
       </c>
       <c r="H231" s="3" t="n">
         <v>0.5926</v>
@@ -14340,7 +14349,7 @@
         <v>0</v>
       </c>
       <c r="L231" s="3" t="n">
-        <v>0.1111</v>
+        <v>0.3333</v>
       </c>
       <c r="M231" s="3" t="n">
         <v>27</v>
@@ -14352,7 +14361,7 @@
         <v>0</v>
       </c>
       <c r="P231" s="3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="232">
@@ -14385,7 +14394,7 @@
         <v>0</v>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H232" s="2" t="n">
         <v>1</v>
@@ -14445,7 +14454,7 @@
         <v>0.3333</v>
       </c>
       <c r="G233" s="3" t="n">
-        <v>0.3333</v>
+        <v>0.1667</v>
       </c>
       <c r="H233" s="3" t="n">
         <v>0.1667</v>
@@ -14460,7 +14469,7 @@
         <v>0</v>
       </c>
       <c r="L233" s="3" t="n">
-        <v>0.3333</v>
+        <v>0.6667</v>
       </c>
       <c r="M233" s="3" t="n">
         <v>6</v>
@@ -14634,7 +14643,7 @@
         <v>0.8333</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>0.1667</v>
+        <v>0.3333</v>
       </c>
       <c r="K236" s="2" t="n">
         <v>0</v>
@@ -14652,7 +14661,7 @@
         <v>0</v>
       </c>
       <c r="P236" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="237">
@@ -14754,7 +14763,7 @@
         <v>0.4286</v>
       </c>
       <c r="J238" s="2" t="n">
-        <v>0.1429</v>
+        <v>0.2857</v>
       </c>
       <c r="K238" s="2" t="n">
         <v>0</v>
@@ -14874,7 +14883,7 @@
         <v>0.5556</v>
       </c>
       <c r="J240" s="2" t="n">
-        <v>0.4444</v>
+        <v>0.5556</v>
       </c>
       <c r="K240" s="2" t="n">
         <v>0</v>
@@ -14889,7 +14898,7 @@
         <v>3.7778</v>
       </c>
       <c r="O240" s="2" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="P240" s="2" t="n">
         <v>0</v>
@@ -14934,7 +14943,7 @@
         <v>0.1</v>
       </c>
       <c r="J241" s="3" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K241" s="3" t="n">
         <v>0</v>
@@ -14994,7 +15003,7 @@
         <v>0.3529</v>
       </c>
       <c r="J242" s="2" t="n">
-        <v>0.4118</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="K242" s="2" t="n">
         <v>0</v>
@@ -15054,13 +15063,13 @@
         <v>0.4286</v>
       </c>
       <c r="J243" s="3" t="n">
-        <v>0.1429</v>
+        <v>0.2857</v>
       </c>
       <c r="K243" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L243" s="3" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.3333</v>
       </c>
       <c r="M243" s="3" t="n">
         <v>14</v>
@@ -15069,7 +15078,7 @@
         <v>5</v>
       </c>
       <c r="O243" s="3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P243" s="3" t="n">
         <v>0</v>
@@ -15120,7 +15129,7 @@
         <v>0</v>
       </c>
       <c r="L244" s="2" t="n">
-        <v>0.09089999999999999</v>
+        <v>1</v>
       </c>
       <c r="M244" s="2" t="n">
         <v>11</v>
@@ -15345,7 +15354,7 @@
         <v>0</v>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="H248" s="2" t="n">
         <v>0.375</v>
@@ -15372,7 +15381,7 @@
         <v>0</v>
       </c>
       <c r="P248" s="2" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="249">
@@ -15474,7 +15483,7 @@
         <v>0.4545</v>
       </c>
       <c r="J250" s="2" t="n">
-        <v>0.4545</v>
+        <v>0.5455</v>
       </c>
       <c r="K250" s="2" t="n">
         <v>0</v>
@@ -15489,10 +15498,10 @@
         <v>4.3636</v>
       </c>
       <c r="O250" s="2" t="n">
-        <v>0.2</v>
+        <v>0.1667</v>
       </c>
       <c r="P250" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -15534,7 +15543,7 @@
         <v>0.5</v>
       </c>
       <c r="J251" s="3" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="K251" s="3" t="n">
         <v>0</v>
@@ -15552,7 +15561,7 @@
         <v>0</v>
       </c>
       <c r="P251" s="3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="252">
@@ -15645,7 +15654,7 @@
         <v>0.1</v>
       </c>
       <c r="G253" s="3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H253" s="3" t="n">
         <v>0.7</v>
@@ -15774,7 +15783,7 @@
         <v>1</v>
       </c>
       <c r="J255" s="3" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K255" s="3" t="n">
         <v>0</v>
@@ -15792,7 +15801,7 @@
         <v>0</v>
       </c>
       <c r="P255" s="3" t="n">
-        <v>0.3333</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="256">
@@ -15912,7 +15921,7 @@
         <v>0</v>
       </c>
       <c r="P257" s="3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="258">
@@ -16194,7 +16203,7 @@
         <v>0.8333</v>
       </c>
       <c r="J262" s="2" t="n">
-        <v>0.75</v>
+        <v>0.8333</v>
       </c>
       <c r="K262" s="2" t="n">
         <v>0</v>
@@ -16212,7 +16221,7 @@
         <v>0</v>
       </c>
       <c r="P262" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="263">
@@ -16374,13 +16383,13 @@
         <v>0.8571</v>
       </c>
       <c r="J265" s="3" t="n">
-        <v>0.4286</v>
+        <v>0.5714</v>
       </c>
       <c r="K265" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L265" s="3" t="n">
-        <v>0.1429</v>
+        <v>1</v>
       </c>
       <c r="M265" s="3" t="n">
         <v>7</v>
@@ -16392,7 +16401,7 @@
         <v>0</v>
       </c>
       <c r="P265" s="3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="266">
@@ -16440,7 +16449,7 @@
         <v>0</v>
       </c>
       <c r="L266" s="2" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="M266" s="2" t="n">
         <v>5</v>
@@ -16614,7 +16623,7 @@
         <v>0.6667</v>
       </c>
       <c r="J269" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6667</v>
       </c>
       <c r="K269" s="3" t="n">
         <v>0</v>
@@ -16629,7 +16638,7 @@
         <v>4.8333</v>
       </c>
       <c r="O269" s="3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P269" s="3" t="n">
         <v>0</v>
@@ -16812,7 +16821,7 @@
         <v>0</v>
       </c>
       <c r="P272" s="2" t="n">
-        <v>0.1667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -16845,7 +16854,7 @@
         <v>0</v>
       </c>
       <c r="G273" s="3" t="n">
-        <v>0.2222</v>
+        <v>0.1111</v>
       </c>
       <c r="H273" s="3" t="n">
         <v>0.2222</v>
@@ -17292,7 +17301,7 @@
         <v>0</v>
       </c>
       <c r="P280" s="2" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281">
@@ -17832,7 +17841,7 @@
         <v>0</v>
       </c>
       <c r="P289" s="3" t="n">
-        <v>0.1667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -18054,7 +18063,7 @@
         <v>0.6</v>
       </c>
       <c r="J293" s="3" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K293" s="3" t="n">
         <v>0</v>
@@ -18072,7 +18081,7 @@
         <v>0</v>
       </c>
       <c r="P293" s="3" t="n">
-        <v>0.1667</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="294">
@@ -18114,7 +18123,7 @@
         <v>0.7778</v>
       </c>
       <c r="J294" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.4444</v>
       </c>
       <c r="K294" s="2" t="n">
         <v>0</v>
@@ -18132,7 +18141,7 @@
         <v>0</v>
       </c>
       <c r="P294" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="295">
@@ -18192,7 +18201,7 @@
         <v>0</v>
       </c>
       <c r="P295" s="3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
@@ -18252,7 +18261,7 @@
         <v>0</v>
       </c>
       <c r="P296" s="2" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -18432,7 +18441,7 @@
         <v>0</v>
       </c>
       <c r="P299" s="3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -18654,7 +18663,7 @@
         <v>0.7222</v>
       </c>
       <c r="J303" s="3" t="n">
-        <v>0.7778</v>
+        <v>0.8333</v>
       </c>
       <c r="K303" s="3" t="n">
         <v>0</v>
@@ -18669,10 +18678,10 @@
         <v>5.0556</v>
       </c>
       <c r="O303" s="3" t="n">
-        <v>0.1429</v>
+        <v>0.1333</v>
       </c>
       <c r="P303" s="3" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
@@ -18954,7 +18963,7 @@
         <v>0.75</v>
       </c>
       <c r="J308" s="2" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="K308" s="2" t="n">
         <v>0</v>
@@ -19005,7 +19014,7 @@
         <v>0.4</v>
       </c>
       <c r="G309" s="3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H309" s="3" t="n">
         <v>0.2</v>
@@ -19020,7 +19029,7 @@
         <v>0</v>
       </c>
       <c r="L309" s="3" t="n">
-        <v>0.2</v>
+        <v>0.3333</v>
       </c>
       <c r="M309" s="3" t="n">
         <v>5</v>
@@ -19074,7 +19083,7 @@
         <v>0.6667</v>
       </c>
       <c r="J310" s="2" t="n">
-        <v>0.4167</v>
+        <v>0.5</v>
       </c>
       <c r="K310" s="2" t="n">
         <v>0</v>
@@ -19089,7 +19098,7 @@
         <v>4.4167</v>
       </c>
       <c r="O310" s="2" t="n">
-        <v>0.2</v>
+        <v>0.3333</v>
       </c>
       <c r="P310" s="2" t="n">
         <v>0</v>
@@ -19212,7 +19221,7 @@
         <v>0</v>
       </c>
       <c r="P312" s="2" t="n">
-        <v>0.1667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
@@ -19365,7 +19374,7 @@
         <v>0</v>
       </c>
       <c r="G315" s="3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H315" s="3" t="n">
         <v>1</v>
@@ -19425,7 +19434,7 @@
         <v>0</v>
       </c>
       <c r="G316" s="2" t="n">
-        <v>0.5714</v>
+        <v>0.2857</v>
       </c>
       <c r="H316" s="2" t="n">
         <v>0.1429</v>
@@ -19545,7 +19554,7 @@
         <v>0</v>
       </c>
       <c r="G318" s="2" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H318" s="2" t="n">
         <v>0.4</v>
@@ -19665,7 +19674,7 @@
         <v>0.1429</v>
       </c>
       <c r="G320" s="2" t="n">
-        <v>0.2857</v>
+        <v>0.1429</v>
       </c>
       <c r="H320" s="2" t="n">
         <v>0.4286</v>
@@ -19680,7 +19689,7 @@
         <v>0</v>
       </c>
       <c r="L320" s="2" t="n">
-        <v>0.1429</v>
+        <v>0.5</v>
       </c>
       <c r="M320" s="2" t="n">
         <v>7</v>
@@ -19725,7 +19734,7 @@
         <v>0.125</v>
       </c>
       <c r="G321" s="3" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="H321" s="3" t="n">
         <v>0.625</v>
@@ -19785,7 +19794,7 @@
         <v>0</v>
       </c>
       <c r="G322" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H322" s="2" t="n">
         <v>0</v>
@@ -19905,7 +19914,7 @@
         <v>0.25</v>
       </c>
       <c r="G324" s="2" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H324" s="2" t="n">
         <v>0.25</v>
@@ -19974,7 +19983,7 @@
         <v>0.9091</v>
       </c>
       <c r="J325" s="3" t="n">
-        <v>0.6364</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="K325" s="3" t="n">
         <v>0</v>
@@ -19989,10 +19998,10 @@
         <v>3.5455</v>
       </c>
       <c r="O325" s="3" t="n">
-        <v>0.1429</v>
+        <v>0.25</v>
       </c>
       <c r="P325" s="3" t="n">
-        <v>0.2857</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="326">
@@ -20034,13 +20043,13 @@
         <v>1</v>
       </c>
       <c r="J326" s="2" t="n">
-        <v>0.4375</v>
+        <v>0.5</v>
       </c>
       <c r="K326" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L326" s="2" t="n">
-        <v>0.0625</v>
+        <v>0.1667</v>
       </c>
       <c r="M326" s="2" t="n">
         <v>16</v>
@@ -20049,10 +20058,10 @@
         <v>5</v>
       </c>
       <c r="O326" s="2" t="n">
-        <v>0.2857</v>
+        <v>0.25</v>
       </c>
       <c r="P326" s="2" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
@@ -20085,7 +20094,7 @@
         <v>0.125</v>
       </c>
       <c r="G327" s="3" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="H327" s="3" t="n">
         <v>0.5</v>
@@ -20094,7 +20103,7 @@
         <v>0.8125</v>
       </c>
       <c r="J327" s="3" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="K327" s="3" t="n">
         <v>0</v>
@@ -20109,10 +20118,10 @@
         <v>4.5</v>
       </c>
       <c r="O327" s="3" t="n">
-        <v>0.1429</v>
+        <v>0.125</v>
       </c>
       <c r="P327" s="3" t="n">
-        <v>0.2143</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="328">
@@ -20154,7 +20163,7 @@
         <v>0.8235</v>
       </c>
       <c r="J328" s="2" t="n">
-        <v>0.6471</v>
+        <v>0.7059</v>
       </c>
       <c r="K328" s="2" t="n">
         <v>0</v>
@@ -20169,10 +20178,10 @@
         <v>4.4118</v>
       </c>
       <c r="O328" s="2" t="n">
-        <v>0</v>
+        <v>0.0833</v>
       </c>
       <c r="P328" s="2" t="n">
-        <v>0.4545</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="329">
@@ -20232,7 +20241,7 @@
         <v>0.0833</v>
       </c>
       <c r="P329" s="3" t="n">
-        <v>0.1667</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="330">
@@ -20265,7 +20274,7 @@
         <v>0.3571</v>
       </c>
       <c r="G330" s="2" t="n">
-        <v>0.2143</v>
+        <v>0.1429</v>
       </c>
       <c r="H330" s="2" t="n">
         <v>0.2857</v>
@@ -20340,7 +20349,7 @@
         <v>0</v>
       </c>
       <c r="L331" s="3" t="n">
-        <v>0.125</v>
+        <v>0.3333</v>
       </c>
       <c r="M331" s="3" t="n">
         <v>16</v>
@@ -20352,7 +20361,7 @@
         <v>0.1</v>
       </c>
       <c r="P331" s="3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="332">
@@ -20460,7 +20469,7 @@
         <v>0</v>
       </c>
       <c r="L333" s="3" t="n">
-        <v>0.2143</v>
+        <v>0.75</v>
       </c>
       <c r="M333" s="3" t="n">
         <v>14</v>
@@ -20472,7 +20481,7 @@
         <v>0.3333</v>
       </c>
       <c r="P333" s="3" t="n">
-        <v>0.1667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334">
@@ -20505,7 +20514,7 @@
         <v>0.5</v>
       </c>
       <c r="G334" s="2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H334" s="2" t="n">
         <v>0.5</v>
@@ -20520,7 +20529,7 @@
         <v>0</v>
       </c>
       <c r="L334" s="2" t="n">
-        <v>0.2</v>
+        <v>0.3333</v>
       </c>
       <c r="M334" s="2" t="n">
         <v>10</v>
@@ -20700,7 +20709,7 @@
         <v>0</v>
       </c>
       <c r="L337" s="3" t="n">
-        <v>0.125</v>
+        <v>0.5</v>
       </c>
       <c r="M337" s="3" t="n">
         <v>8</v>
@@ -20745,7 +20754,7 @@
         <v>0</v>
       </c>
       <c r="G338" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.3333</v>
       </c>
       <c r="H338" s="2" t="n">
         <v>0.6667</v>
@@ -20832,7 +20841,7 @@
         <v>0</v>
       </c>
       <c r="P339" s="3" t="n">
-        <v>0.1667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340">
@@ -20865,7 +20874,7 @@
         <v>0.1818</v>
       </c>
       <c r="G340" s="2" t="n">
-        <v>0.3636</v>
+        <v>0.1818</v>
       </c>
       <c r="H340" s="2" t="n">
         <v>0.2727</v>
@@ -20880,7 +20889,7 @@
         <v>0</v>
       </c>
       <c r="L340" s="2" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="M340" s="2" t="n">
         <v>11</v>
@@ -21105,7 +21114,7 @@
         <v>0</v>
       </c>
       <c r="G344" s="2" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H344" s="2" t="n">
         <v>0.75</v>
@@ -21285,7 +21294,7 @@
         <v>0.2857</v>
       </c>
       <c r="G347" s="3" t="n">
-        <v>0.2857</v>
+        <v>0.1429</v>
       </c>
       <c r="H347" s="3" t="n">
         <v>0.2857</v>
@@ -21300,7 +21309,7 @@
         <v>0</v>
       </c>
       <c r="L347" s="3" t="n">
-        <v>0.1429</v>
+        <v>0.3333</v>
       </c>
       <c r="M347" s="3" t="n">
         <v>7</v>
@@ -21345,7 +21354,7 @@
         <v>0.25</v>
       </c>
       <c r="G348" s="2" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H348" s="2" t="n">
         <v>0.25</v>
@@ -21540,7 +21549,7 @@
         <v>0</v>
       </c>
       <c r="L351" s="3" t="n">
-        <v>0.3333</v>
+        <v>1</v>
       </c>
       <c r="M351" s="3" t="n">
         <v>3</v>
@@ -21660,7 +21669,7 @@
         <v>0</v>
       </c>
       <c r="L353" s="3" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
       <c r="M353" s="3" t="n">
         <v>3</v>
@@ -21732,7 +21741,7 @@
         <v>0</v>
       </c>
       <c r="P354" s="2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355">
@@ -21825,7 +21834,7 @@
         <v>0.1429</v>
       </c>
       <c r="G356" s="2" t="n">
-        <v>0.2857</v>
+        <v>0.1429</v>
       </c>
       <c r="H356" s="2" t="n">
         <v>0.5714</v>
@@ -21960,7 +21969,7 @@
         <v>0</v>
       </c>
       <c r="L358" s="2" t="n">
-        <v>0.1333</v>
+        <v>0.5</v>
       </c>
       <c r="M358" s="2" t="n">
         <v>15</v>
@@ -22065,7 +22074,7 @@
         <v>0</v>
       </c>
       <c r="G360" s="2" t="n">
-        <v>0.1176</v>
+        <v>0.0588</v>
       </c>
       <c r="H360" s="2" t="n">
         <v>0.2941</v>
@@ -22080,7 +22089,7 @@
         <v>0</v>
       </c>
       <c r="L360" s="2" t="n">
-        <v>0.1176</v>
+        <v>1</v>
       </c>
       <c r="M360" s="2" t="n">
         <v>17</v>
@@ -22092,7 +22101,7 @@
         <v>0</v>
       </c>
       <c r="P360" s="2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="361">
@@ -22272,7 +22281,7 @@
         <v>0</v>
       </c>
       <c r="P363" s="3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364">
@@ -22332,7 +22341,7 @@
         <v>0</v>
       </c>
       <c r="P364" s="2" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="365">
@@ -22392,7 +22401,7 @@
         <v>0.0625</v>
       </c>
       <c r="P365" s="3" t="n">
-        <v>0.3125</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="366">
@@ -22434,7 +22443,7 @@
         <v>0.7647</v>
       </c>
       <c r="J366" s="2" t="n">
-        <v>1</v>
+        <v>1.0588</v>
       </c>
       <c r="K366" s="2" t="n">
         <v>0</v>
@@ -22449,10 +22458,10 @@
         <v>4.4118</v>
       </c>
       <c r="O366" s="2" t="n">
-        <v>0.0588</v>
+        <v>0.0556</v>
       </c>
       <c r="P366" s="2" t="n">
-        <v>0.2353</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="367">
@@ -22494,13 +22503,13 @@
         <v>0.8182</v>
       </c>
       <c r="J367" s="3" t="n">
-        <v>1.1818</v>
+        <v>1.2727</v>
       </c>
       <c r="K367" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L367" s="3" t="n">
-        <v>0.09089999999999999</v>
+        <v>1</v>
       </c>
       <c r="M367" s="3" t="n">
         <v>11</v>
@@ -22509,10 +22518,10 @@
         <v>5.3636</v>
       </c>
       <c r="O367" s="3" t="n">
-        <v>0.0769</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="P367" s="3" t="n">
-        <v>0.1538</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="368">
@@ -22614,7 +22623,7 @@
         <v>0.6429</v>
       </c>
       <c r="J369" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714</v>
       </c>
       <c r="K369" s="3" t="n">
         <v>0</v>
@@ -22629,10 +22638,10 @@
         <v>5.0714</v>
       </c>
       <c r="O369" s="3" t="n">
-        <v>0.1429</v>
+        <v>0.125</v>
       </c>
       <c r="P369" s="3" t="n">
-        <v>0.2857</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="370">
@@ -22734,7 +22743,7 @@
         <v>0.7272999999999999</v>
       </c>
       <c r="J371" s="3" t="n">
-        <v>0.6364</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="K371" s="3" t="n">
         <v>0</v>
@@ -22752,7 +22761,7 @@
         <v>0</v>
       </c>
       <c r="P371" s="3" t="n">
-        <v>0.2857</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="372">
@@ -22794,7 +22803,7 @@
         <v>0.4286</v>
       </c>
       <c r="J372" s="2" t="n">
-        <v>0.7143</v>
+        <v>0.8571</v>
       </c>
       <c r="K372" s="2" t="n">
         <v>0</v>
@@ -22854,13 +22863,13 @@
         <v>0.75</v>
       </c>
       <c r="J373" s="3" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="K373" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L373" s="3" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="M373" s="3" t="n">
         <v>4</v>
@@ -22914,7 +22923,7 @@
         <v>0.5</v>
       </c>
       <c r="J374" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6667</v>
       </c>
       <c r="K374" s="2" t="n">
         <v>0</v>
@@ -22974,7 +22983,7 @@
         <v>0.5</v>
       </c>
       <c r="J375" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K375" s="3" t="n">
         <v>0</v>
@@ -23085,7 +23094,7 @@
         <v>0</v>
       </c>
       <c r="G377" s="3" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="H377" s="3" t="n">
         <v>0.2</v>
@@ -23145,7 +23154,7 @@
         <v>0</v>
       </c>
       <c r="G378" s="2" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H378" s="2" t="n">
         <v>0.3333</v>
@@ -23205,7 +23214,7 @@
         <v>0.125</v>
       </c>
       <c r="G379" s="3" t="n">
-        <v>0.375</v>
+        <v>0.1875</v>
       </c>
       <c r="H379" s="3" t="n">
         <v>0.4375</v>
@@ -23220,7 +23229,7 @@
         <v>0</v>
       </c>
       <c r="L379" s="3" t="n">
-        <v>0.1875</v>
+        <v>0.4</v>
       </c>
       <c r="M379" s="3" t="n">
         <v>16</v>
@@ -23280,7 +23289,7 @@
         <v>0</v>
       </c>
       <c r="L380" s="2" t="n">
-        <v>0.0526</v>
+        <v>0.25</v>
       </c>
       <c r="M380" s="2" t="n">
         <v>19</v>
@@ -23325,7 +23334,7 @@
         <v>0.2105</v>
       </c>
       <c r="G381" s="3" t="n">
-        <v>0.1579</v>
+        <v>0.1053</v>
       </c>
       <c r="H381" s="3" t="n">
         <v>0.3158</v>
@@ -23340,7 +23349,7 @@
         <v>0</v>
       </c>
       <c r="L381" s="3" t="n">
-        <v>0.1053</v>
+        <v>0.1667</v>
       </c>
       <c r="M381" s="3" t="n">
         <v>19</v>
@@ -23352,7 +23361,7 @@
         <v>0.1875</v>
       </c>
       <c r="P381" s="3" t="n">
-        <v>0.125</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="382">
@@ -23445,7 +23454,7 @@
         <v>0</v>
       </c>
       <c r="G383" s="3" t="n">
-        <v>0.2353</v>
+        <v>0.1176</v>
       </c>
       <c r="H383" s="3" t="n">
         <v>0.2941</v>
@@ -23454,7 +23463,7 @@
         <v>0.5881999999999999</v>
       </c>
       <c r="J383" s="3" t="n">
-        <v>0.3529</v>
+        <v>0.4706</v>
       </c>
       <c r="K383" s="3" t="n">
         <v>0</v>
@@ -23472,7 +23481,7 @@
         <v>0</v>
       </c>
       <c r="P383" s="3" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
   </sheetData>
